--- a/YSI400.xlsx
+++ b/YSI400.xlsx
@@ -40,6 +40,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -60,7 +61,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,7 +110,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -198,14 +198,14 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0806323385518591"/>
-          <c:y val="0.0372123317412071"/>
-          <c:w val="0.713490704500978"/>
-          <c:h val="0.776812852800695"/>
+          <c:x val="0.0806008426451731"/>
+          <c:y val="0.0371689101172384"/>
+          <c:w val="0.713439579898638"/>
+          <c:h val="0.776726009552757"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
-        <c:scatterStyle val="line"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -215,14 +215,17 @@
               <a:srgbClr val="004586"/>
             </a:solidFill>
             <a:ln w="28800">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+            <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="004586"/>
               </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
+            </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:txPr>
@@ -236,6 +239,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -249,6 +253,21 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="0">
+                <a:solidFill>
+                  <a:srgbClr val="004586"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:forward val="0"/>
+            <c:backward val="0"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$A$2:$A$32</c:f>
@@ -455,17 +474,17 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="15017078"/>
-        <c:axId val="34268282"/>
+        <c:axId val="52315241"/>
+        <c:axId val="83697628"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="15017078"/>
+        <c:axId val="52315241"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -487,12 +506,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34268282"/>
+        <c:crossAx val="83697628"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="34268282"/>
+        <c:axId val="83697628"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -507,7 +526,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -529,9 +548,9 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15017078"/>
+        <c:crossAx val="52315241"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -590,9 +609,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>443520</xdr:colOff>
+      <xdr:colOff>443160</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>73800</xdr:rowOff>
+      <xdr:rowOff>73440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -600,8 +619,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="1872000" y="154800"/>
-        <a:ext cx="5886720" cy="4145400"/>
+        <a:off x="1874520" y="154800"/>
+        <a:ext cx="5895360" cy="4145040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -620,7 +639,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
